--- a/data/trans_camb/P19C07-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C07-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 0,77</t>
+          <t>-2,33; 0,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,39</t>
+          <t>-2,52; 0,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,79</t>
+          <t>-1,74; 1,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; -0,08</t>
+          <t>-2,96; -0,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,25</t>
+          <t>-2,27; 1,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,84</t>
+          <t>-2,12; 1,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,24; -0,15</t>
+          <t>-2,23; -0,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,39</t>
+          <t>-2,08; 0,5</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,71</t>
+          <t>-1,46; 0,79</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-68,62; 55,17</t>
+          <t>-68,08; 55,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-84,91; 40,73</t>
+          <t>-80,45; 31,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-56,69; 106,71</t>
+          <t>-55,81; 110,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-67,98; 2,89</t>
+          <t>-68,93; 0,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-59,48; 46,3</t>
+          <t>-58,42; 45,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,59; 33,44</t>
+          <t>-48,92; 47,98</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,81; -6,12</t>
+          <t>-61,87; -7,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-60,02; 16,07</t>
+          <t>-58,54; 20,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 31,18</t>
+          <t>-41,11; 34,83</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,18</t>
+          <t>-1,98; 1,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,0</t>
+          <t>-1,86; 0,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,0</t>
+          <t>-2,59; 0,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 2,18</t>
+          <t>-0,78; 2,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 1,27</t>
+          <t>-1,25; 1,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 1,29</t>
+          <t>-1,76; 1,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,19</t>
+          <t>-0,86; 1,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,86</t>
+          <t>-1,32; 0,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,67</t>
+          <t>-1,55; 0,82</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,98; 36,81</t>
+          <t>-39,58; 32,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 31,54</t>
+          <t>-38,25; 27,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-50,63; 29,53</t>
+          <t>-51,72; 24,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 68,35</t>
+          <t>-18,14; 63,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 39,83</t>
+          <t>-27,24; 40,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,26; 38,74</t>
+          <t>-35,97; 40,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 33,4</t>
+          <t>-19,52; 35,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 23,63</t>
+          <t>-28,23; 20,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-33,47; 18,45</t>
+          <t>-34,32; 22,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,91</t>
+          <t>-1,27; 4,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,49</t>
+          <t>-3,66; 0,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 2,29</t>
+          <t>-2,15; 2,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 4,94</t>
+          <t>-0,11; 4,67</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,06</t>
+          <t>-1,2; 3,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,56</t>
+          <t>1,05; 5,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 3,71</t>
+          <t>0,19; 3,56</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,23</t>
+          <t>-1,67; 1,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 3,16</t>
+          <t>0,15; 3,26</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,39; 219,19</t>
+          <t>-34,63; 200,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-78,52; 38,67</t>
+          <t>-80,14; 25,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-45,11; 121,38</t>
+          <t>-49,88; 113,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,43; 391,46</t>
+          <t>-15,56; 428,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,77; 262,88</t>
+          <t>-46,7; 278,79</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,21; 472,94</t>
+          <t>19,26; 497,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 200,17</t>
+          <t>4,89; 205,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-52,17; 66,76</t>
+          <t>-50,23; 81,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 175,94</t>
+          <t>1,62; 193,64</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,88</t>
+          <t>-1,07; 1,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,41</t>
+          <t>-1,55; 0,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,88</t>
+          <t>-1,35; 1,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 1,09</t>
+          <t>-0,86; 1,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 0,99</t>
+          <t>-0,84; 1,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 1,38</t>
+          <t>-0,66; 1,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,73</t>
+          <t>-0,62; 0,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,48</t>
+          <t>-0,93; 0,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,88</t>
+          <t>-0,67; 0,82</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 32,19</t>
+          <t>-26,62; 37,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-38,73; 14,1</t>
+          <t>-38,46; 14,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,43; 27,92</t>
+          <t>-34,75; 34,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,32; 37,28</t>
+          <t>-21,88; 33,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 32,67</t>
+          <t>-21,47; 39,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,38; 45,23</t>
+          <t>-17,05; 49,3</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,83; 23,68</t>
+          <t>-16,47; 24,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,15; 15,61</t>
+          <t>-24,67; 13,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-16,66; 28,5</t>
+          <t>-18,31; 26,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C07-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C07-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-0,26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-0,31</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,36</t>
+          <t>-0,28</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,91</t>
+          <t>-2,27; 0,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,38</t>
+          <t>-2,76; 0,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,8</t>
+          <t>-1,97; 1,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; -0,15</t>
+          <t>-3,01; -0,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,23</t>
+          <t>-2,37; 1,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,13</t>
+          <t>-1,86; 1,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,23; -0,2</t>
+          <t>-2,18; -0,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,5</t>
+          <t>-2,03; 0,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,79</t>
+          <t>-1,39; 0,85</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-5,01%</t>
+          <t>-10,35%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-15,99%</t>
+          <t>-9,11%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-11,92%</t>
+          <t>-9,22%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-68,08; 55,28</t>
+          <t>-68,76; 54,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-80,45; 31,05</t>
+          <t>-83,83; 26,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-55,81; 110,48</t>
+          <t>-65,17; 87,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-68,93; 0,83</t>
+          <t>-67,74; -0,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-58,42; 45,61</t>
+          <t>-57,56; 49,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-48,92; 47,98</t>
+          <t>-43,8; 43,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,87; -7,23</t>
+          <t>-61,46; -5,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,54; 20,87</t>
+          <t>-58,09; 19,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-41,11; 34,83</t>
+          <t>-39,35; 34,72</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,71</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>0,39</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>0,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 1,05</t>
+          <t>-1,81; 1,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,87</t>
+          <t>-1,89; 0,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 0,88</t>
+          <t>-1,74; 1,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,07</t>
+          <t>-0,74; 2,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,36</t>
+          <t>-1,45; 1,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,29</t>
+          <t>-1,06; 1,86</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,2</t>
+          <t>-0,84; 1,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,74</t>
+          <t>-1,29; 0,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,82</t>
+          <t>-0,89; 1,11</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-17,52%</t>
+          <t>-4,95%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-4,16%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-10,94%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,58; 32,84</t>
+          <t>-36,55; 36,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,25; 27,83</t>
+          <t>-38,39; 28,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-51,72; 24,11</t>
+          <t>-35,66; 42,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 63,78</t>
+          <t>-16,47; 66,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-27,24; 40,51</t>
+          <t>-30,96; 43,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 40,61</t>
+          <t>-22,08; 57,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 35,5</t>
+          <t>-18,54; 34,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,23; 20,87</t>
+          <t>-27,81; 21,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 22,33</t>
+          <t>-21,03; 32,08</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,24</t>
+          <t>2,95</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,69</t>
+          <t>1,49</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,13</t>
+          <t>-1,02; 3,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 0,34</t>
+          <t>-3,5; 0,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 2,16</t>
+          <t>-2,23; 1,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 4,67</t>
+          <t>-0,25; 5,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 3,15</t>
+          <t>-1,15; 3,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,47</t>
+          <t>0,6; 5,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,56</t>
+          <t>0,04; 3,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,45</t>
+          <t>-1,78; 1,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 3,26</t>
+          <t>-0,16; 2,8</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>156,54%</t>
+          <t>142,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>57,79%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-34,63; 200,33</t>
+          <t>-25,57; 210,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-80,14; 25,4</t>
+          <t>-79,15; 41,77</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-49,88; 113,1</t>
+          <t>-51,81; 97,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-15,56; 428,63</t>
+          <t>-21,3; 420,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-46,7; 278,79</t>
+          <t>-43,13; 335,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,26; 497,84</t>
+          <t>11,9; 470,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,89; 205,36</t>
+          <t>-1,6; 215,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,23; 81,65</t>
+          <t>-52,55; 69,19</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 193,64</t>
+          <t>-4,71; 150,6</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,26</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,73</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,38</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,04</t>
+          <t>-1,13; 0,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,43</t>
+          <t>-1,52; 0,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,0</t>
+          <t>-1,03; 1,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,02</t>
+          <t>-0,8; 1,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 1,12</t>
+          <t>-0,81; 1,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,46</t>
+          <t>-0,21; 1,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 0,74</t>
+          <t>-0,69; 0,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,4</t>
+          <t>-0,92; 0,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,82</t>
+          <t>-0,37; 1,11</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-7,55%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>11,07%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-26,62; 37,68</t>
+          <t>-27,94; 29,75</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-38,46; 14,66</t>
+          <t>-38,5; 13,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,75; 34,5</t>
+          <t>-25,77; 38,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-21,88; 33,22</t>
+          <t>-19,55; 37,93</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-21,47; 39,08</t>
+          <t>-21,38; 35,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 49,3</t>
+          <t>-5,68; 56,06</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-16,47; 24,86</t>
+          <t>-17,62; 24,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 13,58</t>
+          <t>-23,88; 15,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-18,31; 26,59</t>
+          <t>-9,51; 36,03</t>
         </is>
       </c>
     </row>
